--- a/.schema/MHR_USER_POS.xlsx
+++ b/.schema/MHR_USER_POS.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29530"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\KTC0966\git\sample\.schema\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{8A77C211-FD16-4F30-85FB-4F3FD3D9AFDE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{918D5FA0-6AF8-4A0F-9F74-1AFC8FD0B941}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="57480" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{B6F4095F-5D80-4014-804A-C29E3E77DB6B}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{101276A5-A053-4AE5-A5CD-CD1CB8B7831F}"/>
   </bookViews>
   <sheets>
     <sheet name="EMARF.MHR_USER_POS" sheetId="2" r:id="rId1"/>
@@ -38,9 +38,9 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="10">
-  <si>
-    <t>0001/01/01</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="11">
+  <si>
+    <t>« NULL »</t>
   </si>
   <si>
     <t>UPDATE_USER_ID</t>
@@ -68,6 +68,9 @@
   </si>
   <si>
     <t>BUSHO_ID</t>
+  </si>
+  <si>
+    <t>oracle/XEPDB1：emarf : 2026/03/05 17:34:55</t>
   </si>
 </sst>
 </file>
@@ -75,7 +78,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="176" formatCode="yyyy/mm/dd\ h:mm:ss.000"/>
+    <numFmt numFmtId="176" formatCode="yyyy/mm/dd\ h:mm:ss"/>
   </numFmts>
   <fonts count="5" x14ac:knownFonts="1">
     <font>
@@ -162,7 +165,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -178,16 +181,13 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="標準" xfId="0" builtinId="0"/>
-    <cellStyle name="標準 2" xfId="1" xr:uid="{48B1F86F-6A0E-48C6-AE62-02BACE93072B}"/>
+    <cellStyle name="標準 2" xfId="1" xr:uid="{059B1AF6-F14A-4EF6-A377-B35DF590D376}"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -498,48 +498,53 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{08671DA4-71B2-462D-B41B-F39B222F489A}">
-  <dimension ref="A2:I3"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D170FB04-F170-4F23-9862-009C6D7EA8AB}">
+  <dimension ref="A1:I11"/>
   <sheetFormatPr defaultRowHeight="13.2" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="13.5" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="14" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="11.5" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="13.59765625" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="18.69921875" style="1" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="13.09765625" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="22.5" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="18.69921875" style="1" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="19.8984375" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="22.5" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="18.69921875" style="1" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="20.69921875" style="1" bestFit="1" customWidth="1"/>
     <col min="10" max="16384" width="8.796875" style="1"/>
   </cols>
   <sheetData>
+    <row r="1" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A1" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="A2" s="6" t="s">
+      <c r="A2" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="B2" s="6" t="s">
+      <c r="B2" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="C2" s="6" t="s">
+      <c r="C2" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="D2" s="6" t="s">
+      <c r="D2" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="E2" s="6" t="s">
+      <c r="E2" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="F2" s="6" t="s">
+      <c r="F2" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="G2" s="6" t="s">
+      <c r="G2" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="H2" s="6" t="s">
+      <c r="H2" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="I2" s="6" t="s">
+      <c r="I2" s="5" t="s">
         <v>1</v>
       </c>
     </row>
@@ -553,21 +558,259 @@
       <c r="C3" s="2">
         <v>0</v>
       </c>
-      <c r="D3" s="5" t="s">
-        <v>0</v>
-      </c>
-      <c r="E3" s="4"/>
-      <c r="F3" s="3"/>
+      <c r="D3" s="3">
+        <v>46086</v>
+      </c>
+      <c r="E3" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="F3" s="3">
+        <v>46086</v>
+      </c>
       <c r="G3" s="2">
         <v>0</v>
       </c>
-      <c r="H3" s="3"/>
+      <c r="H3" s="3">
+        <v>46086</v>
+      </c>
       <c r="I3" s="2">
         <v>0</v>
       </c>
     </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A4" s="2">
+        <v>1</v>
+      </c>
+      <c r="B4" s="2">
+        <v>0</v>
+      </c>
+      <c r="C4" s="2">
+        <v>1</v>
+      </c>
+      <c r="D4" s="3">
+        <v>46086</v>
+      </c>
+      <c r="E4" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="F4" s="3">
+        <v>46086</v>
+      </c>
+      <c r="G4" s="2">
+        <v>0</v>
+      </c>
+      <c r="H4" s="3">
+        <v>46086</v>
+      </c>
+      <c r="I4" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A5" s="2">
+        <v>2</v>
+      </c>
+      <c r="B5" s="2">
+        <v>0</v>
+      </c>
+      <c r="C5" s="2">
+        <v>2</v>
+      </c>
+      <c r="D5" s="3">
+        <v>46086</v>
+      </c>
+      <c r="E5" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="F5" s="3">
+        <v>46086</v>
+      </c>
+      <c r="G5" s="2">
+        <v>0</v>
+      </c>
+      <c r="H5" s="3">
+        <v>46086</v>
+      </c>
+      <c r="I5" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A6" s="2">
+        <v>3</v>
+      </c>
+      <c r="B6" s="2">
+        <v>0</v>
+      </c>
+      <c r="C6" s="2">
+        <v>3</v>
+      </c>
+      <c r="D6" s="3">
+        <v>46086</v>
+      </c>
+      <c r="E6" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="F6" s="3">
+        <v>46086</v>
+      </c>
+      <c r="G6" s="2">
+        <v>0</v>
+      </c>
+      <c r="H6" s="3">
+        <v>46086</v>
+      </c>
+      <c r="I6" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A7" s="2">
+        <v>4</v>
+      </c>
+      <c r="B7" s="2">
+        <v>0</v>
+      </c>
+      <c r="C7" s="2">
+        <v>4</v>
+      </c>
+      <c r="D7" s="3">
+        <v>46086</v>
+      </c>
+      <c r="E7" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="F7" s="3">
+        <v>46086</v>
+      </c>
+      <c r="G7" s="2">
+        <v>0</v>
+      </c>
+      <c r="H7" s="3">
+        <v>46086</v>
+      </c>
+      <c r="I7" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A8" s="2">
+        <v>5</v>
+      </c>
+      <c r="B8" s="2">
+        <v>0</v>
+      </c>
+      <c r="C8" s="2">
+        <v>5</v>
+      </c>
+      <c r="D8" s="3">
+        <v>46086</v>
+      </c>
+      <c r="E8" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="F8" s="3">
+        <v>46086</v>
+      </c>
+      <c r="G8" s="2">
+        <v>0</v>
+      </c>
+      <c r="H8" s="3">
+        <v>46086</v>
+      </c>
+      <c r="I8" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A9" s="2">
+        <v>6</v>
+      </c>
+      <c r="B9" s="2">
+        <v>0</v>
+      </c>
+      <c r="C9" s="2">
+        <v>6</v>
+      </c>
+      <c r="D9" s="3">
+        <v>46086</v>
+      </c>
+      <c r="E9" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="F9" s="3">
+        <v>46086</v>
+      </c>
+      <c r="G9" s="2">
+        <v>0</v>
+      </c>
+      <c r="H9" s="3">
+        <v>46086</v>
+      </c>
+      <c r="I9" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A10" s="2">
+        <v>7</v>
+      </c>
+      <c r="B10" s="2">
+        <v>0</v>
+      </c>
+      <c r="C10" s="2">
+        <v>7</v>
+      </c>
+      <c r="D10" s="3">
+        <v>46086</v>
+      </c>
+      <c r="E10" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="F10" s="3">
+        <v>46086</v>
+      </c>
+      <c r="G10" s="2">
+        <v>0</v>
+      </c>
+      <c r="H10" s="3">
+        <v>46086</v>
+      </c>
+      <c r="I10" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A11" s="2">
+        <v>8</v>
+      </c>
+      <c r="B11" s="2">
+        <v>0</v>
+      </c>
+      <c r="C11" s="2">
+        <v>8</v>
+      </c>
+      <c r="D11" s="3">
+        <v>46086</v>
+      </c>
+      <c r="E11" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="F11" s="3">
+        <v>46086</v>
+      </c>
+      <c r="G11" s="2">
+        <v>0</v>
+      </c>
+      <c r="H11" s="3">
+        <v>46086</v>
+      </c>
+      <c r="I11" s="2">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A2:I3" xr:uid="{7F165372-489A-4683-9ACF-9E7BE09C7DE2}"/>
+  <autoFilter ref="A2:I3" xr:uid="{BD5F7D62-02F7-407F-9A77-0123A841F857}"/>
   <phoneticPr fontId="2"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/.schema/MHR_USER_POS.xlsx
+++ b/.schema/MHR_USER_POS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\KTC0966\git\sample\.schema\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{918D5FA0-6AF8-4A0F-9F74-1AFC8FD0B941}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B826F3B4-F81E-4724-8B7C-8FAE19E8C3D6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{101276A5-A053-4AE5-A5CD-CD1CB8B7831F}"/>
   </bookViews>
@@ -559,19 +559,22 @@
         <v>0</v>
       </c>
       <c r="D3" s="3">
-        <v>46086</v>
+        <f t="shared" ref="D3:F11" ca="1" si="0">NOW()</f>
+        <v>46087.424292939817</v>
       </c>
       <c r="E3" s="4" t="s">
         <v>0</v>
       </c>
       <c r="F3" s="3">
-        <v>46086</v>
+        <f ca="1">NOW()</f>
+        <v>46087.424292939817</v>
       </c>
       <c r="G3" s="2">
         <v>0</v>
       </c>
       <c r="H3" s="3">
-        <v>46086</v>
+        <f t="shared" ref="H3:H11" ca="1" si="1">NOW()</f>
+        <v>46087.424292939817</v>
       </c>
       <c r="I3" s="2">
         <v>0</v>
@@ -579,28 +582,31 @@
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A4" s="2">
+        <v>0</v>
+      </c>
+      <c r="B4" s="2">
         <v>1</v>
-      </c>
-      <c r="B4" s="2">
-        <v>0</v>
       </c>
       <c r="C4" s="2">
         <v>1</v>
       </c>
       <c r="D4" s="3">
-        <v>46086</v>
+        <f t="shared" ca="1" si="0"/>
+        <v>46087.424292939817</v>
       </c>
       <c r="E4" s="4" t="s">
         <v>0</v>
       </c>
       <c r="F4" s="3">
-        <v>46086</v>
+        <f t="shared" ca="1" si="0"/>
+        <v>46087.424292939817</v>
       </c>
       <c r="G4" s="2">
         <v>0</v>
       </c>
       <c r="H4" s="3">
-        <v>46086</v>
+        <f t="shared" ca="1" si="1"/>
+        <v>46087.424292939817</v>
       </c>
       <c r="I4" s="2">
         <v>0</v>
@@ -608,28 +614,31 @@
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A5" s="2">
+        <v>0</v>
+      </c>
+      <c r="B5" s="2">
         <v>2</v>
-      </c>
-      <c r="B5" s="2">
-        <v>0</v>
       </c>
       <c r="C5" s="2">
         <v>2</v>
       </c>
       <c r="D5" s="3">
-        <v>46086</v>
+        <f t="shared" ca="1" si="0"/>
+        <v>46087.424292939817</v>
       </c>
       <c r="E5" s="4" t="s">
         <v>0</v>
       </c>
       <c r="F5" s="3">
-        <v>46086</v>
+        <f t="shared" ca="1" si="0"/>
+        <v>46087.424292939817</v>
       </c>
       <c r="G5" s="2">
         <v>0</v>
       </c>
       <c r="H5" s="3">
-        <v>46086</v>
+        <f t="shared" ca="1" si="1"/>
+        <v>46087.424292939817</v>
       </c>
       <c r="I5" s="2">
         <v>0</v>
@@ -637,28 +646,31 @@
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A6" s="2">
+        <v>0</v>
+      </c>
+      <c r="B6" s="2">
         <v>3</v>
-      </c>
-      <c r="B6" s="2">
-        <v>0</v>
       </c>
       <c r="C6" s="2">
         <v>3</v>
       </c>
       <c r="D6" s="3">
-        <v>46086</v>
+        <f t="shared" ca="1" si="0"/>
+        <v>46087.424292939817</v>
       </c>
       <c r="E6" s="4" t="s">
         <v>0</v>
       </c>
       <c r="F6" s="3">
-        <v>46086</v>
+        <f t="shared" ca="1" si="0"/>
+        <v>46087.424292939817</v>
       </c>
       <c r="G6" s="2">
         <v>0</v>
       </c>
       <c r="H6" s="3">
-        <v>46086</v>
+        <f t="shared" ca="1" si="1"/>
+        <v>46087.424292939817</v>
       </c>
       <c r="I6" s="2">
         <v>0</v>
@@ -666,28 +678,31 @@
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A7" s="2">
+        <v>0</v>
+      </c>
+      <c r="B7" s="2">
         <v>4</v>
-      </c>
-      <c r="B7" s="2">
-        <v>0</v>
       </c>
       <c r="C7" s="2">
         <v>4</v>
       </c>
       <c r="D7" s="3">
-        <v>46086</v>
+        <f t="shared" ca="1" si="0"/>
+        <v>46087.424292939817</v>
       </c>
       <c r="E7" s="4" t="s">
         <v>0</v>
       </c>
       <c r="F7" s="3">
-        <v>46086</v>
+        <f t="shared" ca="1" si="0"/>
+        <v>46087.424292939817</v>
       </c>
       <c r="G7" s="2">
         <v>0</v>
       </c>
       <c r="H7" s="3">
-        <v>46086</v>
+        <f t="shared" ca="1" si="1"/>
+        <v>46087.424292939817</v>
       </c>
       <c r="I7" s="2">
         <v>0</v>
@@ -695,28 +710,31 @@
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A8" s="2">
+        <v>0</v>
+      </c>
+      <c r="B8" s="2">
         <v>5</v>
-      </c>
-      <c r="B8" s="2">
-        <v>0</v>
       </c>
       <c r="C8" s="2">
         <v>5</v>
       </c>
       <c r="D8" s="3">
-        <v>46086</v>
+        <f t="shared" ca="1" si="0"/>
+        <v>46087.424292939817</v>
       </c>
       <c r="E8" s="4" t="s">
         <v>0</v>
       </c>
       <c r="F8" s="3">
-        <v>46086</v>
+        <f t="shared" ca="1" si="0"/>
+        <v>46087.424292939817</v>
       </c>
       <c r="G8" s="2">
         <v>0</v>
       </c>
       <c r="H8" s="3">
-        <v>46086</v>
+        <f t="shared" ca="1" si="1"/>
+        <v>46087.424292939817</v>
       </c>
       <c r="I8" s="2">
         <v>0</v>
@@ -724,28 +742,31 @@
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A9" s="2">
+        <v>0</v>
+      </c>
+      <c r="B9" s="2">
         <v>6</v>
-      </c>
-      <c r="B9" s="2">
-        <v>0</v>
       </c>
       <c r="C9" s="2">
         <v>6</v>
       </c>
       <c r="D9" s="3">
-        <v>46086</v>
+        <f t="shared" ca="1" si="0"/>
+        <v>46087.424292939817</v>
       </c>
       <c r="E9" s="4" t="s">
         <v>0</v>
       </c>
       <c r="F9" s="3">
-        <v>46086</v>
+        <f t="shared" ca="1" si="0"/>
+        <v>46087.424292939817</v>
       </c>
       <c r="G9" s="2">
         <v>0</v>
       </c>
       <c r="H9" s="3">
-        <v>46086</v>
+        <f t="shared" ca="1" si="1"/>
+        <v>46087.424292939817</v>
       </c>
       <c r="I9" s="2">
         <v>0</v>
@@ -753,28 +774,31 @@
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A10" s="2">
+        <v>0</v>
+      </c>
+      <c r="B10" s="2">
         <v>7</v>
-      </c>
-      <c r="B10" s="2">
-        <v>0</v>
       </c>
       <c r="C10" s="2">
         <v>7</v>
       </c>
       <c r="D10" s="3">
-        <v>46086</v>
+        <f t="shared" ca="1" si="0"/>
+        <v>46087.424292939817</v>
       </c>
       <c r="E10" s="4" t="s">
         <v>0</v>
       </c>
       <c r="F10" s="3">
-        <v>46086</v>
+        <f t="shared" ca="1" si="0"/>
+        <v>46087.424292939817</v>
       </c>
       <c r="G10" s="2">
         <v>0</v>
       </c>
       <c r="H10" s="3">
-        <v>46086</v>
+        <f t="shared" ca="1" si="1"/>
+        <v>46087.424292939817</v>
       </c>
       <c r="I10" s="2">
         <v>0</v>
@@ -782,28 +806,31 @@
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A11" s="2">
+        <v>0</v>
+      </c>
+      <c r="B11" s="2">
         <v>8</v>
-      </c>
-      <c r="B11" s="2">
-        <v>0</v>
       </c>
       <c r="C11" s="2">
         <v>8</v>
       </c>
       <c r="D11" s="3">
-        <v>46086</v>
+        <f t="shared" ca="1" si="0"/>
+        <v>46087.424292939817</v>
       </c>
       <c r="E11" s="4" t="s">
         <v>0</v>
       </c>
       <c r="F11" s="3">
-        <v>46086</v>
+        <f t="shared" ca="1" si="0"/>
+        <v>46087.424292939817</v>
       </c>
       <c r="G11" s="2">
         <v>0</v>
       </c>
       <c r="H11" s="3">
-        <v>46086</v>
+        <f t="shared" ca="1" si="1"/>
+        <v>46087.424292939817</v>
       </c>
       <c r="I11" s="2">
         <v>0</v>

--- a/.schema/MHR_USER_POS.xlsx
+++ b/.schema/MHR_USER_POS.xlsx
@@ -1,35 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
-  <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\KTC0966\git\sample\.schema\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="11_8DBC10A1C79A78EB1CC042D1E462C4C2FC332913" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="Calc"/>
+  <workbookPr backupFile="false" showObjects="all" date1904="false"/>
+  <workbookProtection/>
   <bookViews>
-    <workbookView xWindow="57480" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
   </bookViews>
   <sheets>
-    <sheet name="EMARF.MHR_USER_POS" sheetId="1" r:id="rId1"/>
+    <sheet name="EMARF.MHR_USER_POS" sheetId="1" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">EMARF.MHR_USER_POS!$A$2:$I$3</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="0">EMARF.MHR_USER_POS!$2:$2</definedName>
+    <definedName function="false" hidden="false" localSheetId="0" name="_xlnm.Print_Titles" vbProcedure="false">'EMARF.MHR_USER_POS'!$2:$2</definedName>
+    <definedName function="false" hidden="true" localSheetId="0" name="_xlnm._FilterDatabase" vbProcedure="false">'EMARF.MHR_USER_POS'!$A$2:$I$3</definedName>
   </definedNames>
-  <calcPr calcId="191029" iterateDelta="1E-4"/>
+  <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
     <ext xmlns:loext="http://schemas.libreoffice.org/" uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
       <loext:extCalcPr stringRefSyntax="ExcelA1"/>
     </ext>
@@ -40,52 +26,72 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="11">
   <si>
-    <t>oracle/XEPDB1：emarf : 2026/03/05 17:34:55</t>
-  </si>
-  <si>
-    <t>BUSHO_ID</t>
-  </si>
-  <si>
-    <t>SHOKUI_ID</t>
-  </si>
-  <si>
-    <t>USER_ID</t>
-  </si>
-  <si>
-    <t>TEKIYO_BI</t>
-  </si>
-  <si>
-    <t>HAISHI_BI</t>
-  </si>
-  <si>
-    <t>INSERT_TS</t>
-  </si>
-  <si>
-    <t>INSERT_USER_ID</t>
-  </si>
-  <si>
-    <t>UPDATE_TS</t>
-  </si>
-  <si>
-    <t>UPDATE_USER_ID</t>
-  </si>
-  <si>
-    <t>« NULL »</t>
+    <t xml:space="preserve">oracle/XEPDB1：emarf : 2026/03/05 17:34:55</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BUSHO_ID</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SHOKUI_ID</t>
+  </si>
+  <si>
+    <t xml:space="preserve">USER_ID</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TEKIYO_BI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HAISHI_BI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">INSERT_TS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">INSERT_USER_ID</t>
+  </si>
+  <si>
+    <t xml:space="preserve">UPDATE_TS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">UPDATE_USER_ID</t>
+  </si>
+  <si>
+    <t xml:space="preserve">« NULL »</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="1">
-    <numFmt numFmtId="176" formatCode="yyyy/mm/dd\ h:mm:ss"/>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="3">
+    <numFmt numFmtId="164" formatCode="General"/>
+    <numFmt numFmtId="165" formatCode="0"/>
+    <numFmt numFmtId="166" formatCode="yyyy/mm/dd\ h:mm:ss"/>
   </numFmts>
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="7">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="游ゴシック"/>
       <family val="2"/>
+      <charset val="128"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="0"/>
+      <charset val="128"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="0"/>
+      <charset val="128"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="0"/>
       <charset val="128"/>
     </font>
     <font>
@@ -96,7 +102,7 @@
       <charset val="128"/>
     </font>
     <font>
-      <b/>
+      <b val="true"/>
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="ＭＳ Ｐゴシック"/>
@@ -108,12 +114,6 @@
       <color rgb="FFC0C0C0"/>
       <name val="ＭＳ Ｐゴシック"/>
       <family val="3"/>
-      <charset val="128"/>
-    </font>
-    <font>
-      <sz val="6"/>
-      <name val="游ゴシック"/>
-      <family val="2"/>
       <charset val="128"/>
     </font>
   </fonts>
@@ -132,63 +132,117 @@
     </fill>
   </fills>
   <borders count="2">
-    <border>
+    <border diagonalUp="false" diagonalDown="false">
       <left/>
       <right/>
       <top/>
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
+    <border diagonalUp="false" diagonalDown="false">
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="2">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
-      <alignment vertical="center"/>
+  <cellStyleXfs count="21">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyBorder="0" applyProtection="0">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
     </xf>
   </cellStyleXfs>
   <cellXfs count="6">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
-      <alignment vertical="center"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyBorder="1" applyProtection="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="164" fontId="5" fillId="2" borderId="1" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="1" fontId="1" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyBorder="1" applyProtection="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="1" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="176" fontId="1" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyBorder="1" applyProtection="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="166" fontId="4" fillId="0" borderId="1" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyProtection="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="1" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
     </xf>
   </cellXfs>
-  <cellStyles count="2">
-    <cellStyle name="標準" xfId="0" builtinId="0"/>
-    <cellStyle name="標準 2" xfId="1" xr:uid="{00000000-0005-0000-0000-000006000000}"/>
+  <cellStyles count="7">
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Comma" xfId="15" builtinId="3"/>
+    <cellStyle name="Comma [0]" xfId="16" builtinId="6"/>
+    <cellStyle name="Currency" xfId="17" builtinId="4"/>
+    <cellStyle name="Currency [0]" xfId="18" builtinId="7"/>
+    <cellStyle name="Percent" xfId="19" builtinId="5"/>
+    <cellStyle name="標準 2" xfId="20"/>
   </cellStyles>
-  <dxfs count="0"/>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <dxfs count="4">
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF87E7AD"/>
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF000000"/>
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFC0C0C0"/>
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+  </dxfs>
   <colors>
     <indexedColors>
       <rgbColor rgb="FF000000"/>
@@ -247,76 +301,64 @@
       <rgbColor rgb="FF993366"/>
       <rgbColor rgb="FF333399"/>
       <rgbColor rgb="FF333333"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
     </indexedColors>
   </colors>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
 </styleSheet>
 </file>
 
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships"/>
+</file>
+
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office テーマ">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Office テーマ">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
         <a:srgbClr val="000000"/>
       </a:dk1>
       <a:lt1>
-        <a:srgbClr val="FFFFFF"/>
+        <a:srgbClr val="ffffff"/>
       </a:lt1>
       <a:dk2>
-        <a:srgbClr val="44546A"/>
+        <a:srgbClr val="44546a"/>
       </a:dk2>
       <a:lt2>
-        <a:srgbClr val="E7E6E6"/>
+        <a:srgbClr val="e7e6e6"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="4472C4"/>
+        <a:srgbClr val="4472c4"/>
       </a:accent1>
       <a:accent2>
-        <a:srgbClr val="ED7D31"/>
+        <a:srgbClr val="ed7d31"/>
       </a:accent2>
       <a:accent3>
-        <a:srgbClr val="A5A5A5"/>
+        <a:srgbClr val="a5a5a5"/>
       </a:accent3>
       <a:accent4>
-        <a:srgbClr val="FFC000"/>
+        <a:srgbClr val="ffc000"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="5B9BD5"/>
+        <a:srgbClr val="5b9bd5"/>
       </a:accent5>
       <a:accent6>
-        <a:srgbClr val="70AD47"/>
+        <a:srgbClr val="70ad47"/>
       </a:accent6>
       <a:hlink>
-        <a:srgbClr val="0563C1"/>
+        <a:srgbClr val="0563c1"/>
       </a:hlink>
       <a:folHlink>
-        <a:srgbClr val="954F72"/>
+        <a:srgbClr val="954f72"/>
       </a:folHlink>
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
+        <a:latin typeface="Calibri Light" panose="020F0302020204030204" pitchFamily="0" charset="1"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri" panose="020F0502020204030204" pitchFamily="0" charset="1"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
       </a:minorFont>
@@ -348,7 +390,7 @@
             </a:gs>
           </a:gsLst>
           <a:lin ang="5400000" scaled="0"/>
-          <a:tileRect/>
+          <a:tileRect l="0" t="0" r="0" b="0"/>
         </a:gradFill>
         <a:gradFill>
           <a:gsLst>
@@ -372,7 +414,7 @@
             </a:gs>
           </a:gsLst>
           <a:lin ang="5400000" scaled="0"/>
-          <a:tileRect/>
+          <a:tileRect l="0" t="0" r="0" b="0"/>
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
@@ -432,39 +474,40 @@
             </a:gs>
           </a:gsLst>
           <a:lin ang="5400000" scaled="0"/>
-          <a:tileRect/>
+          <a:tileRect l="0" t="0" r="0" b="0"/>
         </a:gradFill>
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
-  <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
   <dimension ref="A1:I11"/>
-  <sheetFormatPr defaultColWidth="8.796875" defaultRowHeight="12.75" customHeight="1" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultColWidth="8.796875" defaultRowHeight="12.75" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col min="1" max="1" width="13.5" style="1" customWidth="1"/>
-    <col min="2" max="2" width="14" style="1" customWidth="1"/>
-    <col min="3" max="3" width="11.5" style="1" customWidth="1"/>
-    <col min="4" max="4" width="18.69921875" style="1" customWidth="1"/>
-    <col min="5" max="5" width="13.09765625" style="1" customWidth="1"/>
-    <col min="6" max="6" width="18.69921875" style="1" customWidth="1"/>
-    <col min="7" max="7" width="19.8984375" style="1" customWidth="1"/>
-    <col min="8" max="8" width="18.69921875" style="1" customWidth="1"/>
-    <col min="9" max="9" width="20.69921875" style="1" customWidth="1"/>
-    <col min="10" max="16384" width="8.796875" style="1"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="13.5"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="11.5"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="18.69"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="13.1"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="18.69"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="19.9"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="1" width="18.69"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="1" width="20.7"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="16384" min="10" style="1" width="8.8"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="13.2" x14ac:dyDescent="0.45">
+    <row r="1" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:9" ht="13.2" x14ac:dyDescent="0.45">
+    <row r="2" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
         <v>1</v>
       </c>
@@ -493,302 +536,303 @@
         <v>9</v>
       </c>
     </row>
-    <row r="3" spans="1:9" ht="13.2" x14ac:dyDescent="0.45">
-      <c r="A3" s="3">
-        <v>0</v>
-      </c>
-      <c r="B3" s="3">
-        <v>0</v>
-      </c>
-      <c r="C3" s="3">
-        <v>0</v>
-      </c>
-      <c r="D3" s="4">
-        <f t="shared" ref="D3:D11" ca="1" si="0">NOW()</f>
-        <v>46090.369605671294</v>
+    <row r="3" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="B3" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C3" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D3" s="4" t="n">
+        <f aca="true">NOW()</f>
+        <v>46091.8634306975</v>
       </c>
       <c r="E3" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="F3" s="4">
-        <f t="shared" ref="F3:F11" ca="1" si="1">NOW()</f>
-        <v>46090.369605671294</v>
-      </c>
-      <c r="G3" s="3">
-        <v>0</v>
-      </c>
-      <c r="H3" s="4">
-        <f t="shared" ref="H3:H11" ca="1" si="2">NOW()</f>
-        <v>46090.369605671294</v>
-      </c>
-      <c r="I3" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:9" ht="13.2" x14ac:dyDescent="0.45">
-      <c r="A4" s="3">
-        <v>0</v>
-      </c>
-      <c r="B4" s="3">
+      <c r="F3" s="4" t="n">
+        <f aca="true">NOW()</f>
+        <v>46091.8634306981</v>
+      </c>
+      <c r="G3" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H3" s="4" t="n">
+        <f aca="true">NOW()</f>
+        <v>46091.8634306985</v>
+      </c>
+      <c r="I3" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="B4" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="C4" s="3">
+      <c r="C4" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="D4" s="4">
-        <f t="shared" ca="1" si="0"/>
-        <v>46090.369605671294</v>
+      <c r="D4" s="4" t="n">
+        <f aca="true">NOW()</f>
+        <v>46091.8634306977</v>
       </c>
       <c r="E4" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="F4" s="4">
-        <f t="shared" ca="1" si="1"/>
-        <v>46090.369605671294</v>
-      </c>
-      <c r="G4" s="3">
-        <v>0</v>
-      </c>
-      <c r="H4" s="4">
-        <f t="shared" ca="1" si="2"/>
-        <v>46090.369605671294</v>
-      </c>
-      <c r="I4" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:9" ht="13.2" x14ac:dyDescent="0.45">
-      <c r="A5" s="3">
-        <v>0</v>
-      </c>
-      <c r="B5" s="3">
+      <c r="F4" s="4" t="n">
+        <f aca="true">NOW()</f>
+        <v>46091.8634306981</v>
+      </c>
+      <c r="G4" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H4" s="4" t="n">
+        <f aca="true">NOW()</f>
+        <v>46091.8634306986</v>
+      </c>
+      <c r="I4" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="B5" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="C5" s="3">
+      <c r="C5" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="D5" s="4">
-        <f t="shared" ca="1" si="0"/>
-        <v>46090.369605671294</v>
+      <c r="D5" s="4" t="n">
+        <f aca="true">NOW()</f>
+        <v>46091.8634306977</v>
       </c>
       <c r="E5" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="F5" s="4">
-        <f t="shared" ca="1" si="1"/>
-        <v>46090.369605671294</v>
-      </c>
-      <c r="G5" s="3">
-        <v>0</v>
-      </c>
-      <c r="H5" s="4">
-        <f t="shared" ca="1" si="2"/>
-        <v>46090.369605671294</v>
-      </c>
-      <c r="I5" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" spans="1:9" ht="13.2" x14ac:dyDescent="0.45">
-      <c r="A6" s="3">
-        <v>0</v>
-      </c>
-      <c r="B6" s="3">
+      <c r="F5" s="4" t="n">
+        <f aca="true">NOW()</f>
+        <v>46091.8634306982</v>
+      </c>
+      <c r="G5" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H5" s="4" t="n">
+        <f aca="true">NOW()</f>
+        <v>46091.8634306986</v>
+      </c>
+      <c r="I5" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="B6" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="C6" s="3">
+      <c r="C6" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="D6" s="4">
-        <f t="shared" ca="1" si="0"/>
-        <v>46090.369605671294</v>
+      <c r="D6" s="4" t="n">
+        <f aca="true">NOW()</f>
+        <v>46091.8634306978</v>
       </c>
       <c r="E6" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="F6" s="4">
-        <f t="shared" ca="1" si="1"/>
-        <v>46090.369605671294</v>
-      </c>
-      <c r="G6" s="3">
-        <v>0</v>
-      </c>
-      <c r="H6" s="4">
-        <f t="shared" ca="1" si="2"/>
-        <v>46090.369605671294</v>
-      </c>
-      <c r="I6" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="1:9" ht="13.2" x14ac:dyDescent="0.45">
-      <c r="A7" s="3">
-        <v>0</v>
-      </c>
-      <c r="B7" s="3">
+      <c r="F6" s="4" t="n">
+        <f aca="true">NOW()</f>
+        <v>46091.8634306982</v>
+      </c>
+      <c r="G6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H6" s="4" t="n">
+        <f aca="true">NOW()</f>
+        <v>46091.8634306987</v>
+      </c>
+      <c r="I6" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="B7" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="C7" s="3">
+      <c r="C7" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="D7" s="4">
-        <f t="shared" ca="1" si="0"/>
-        <v>46090.369605671294</v>
+      <c r="D7" s="4" t="n">
+        <f aca="true">NOW()</f>
+        <v>46091.8634306978</v>
       </c>
       <c r="E7" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="F7" s="4">
-        <f t="shared" ca="1" si="1"/>
-        <v>46090.369605671294</v>
-      </c>
-      <c r="G7" s="3">
-        <v>0</v>
-      </c>
-      <c r="H7" s="4">
-        <f t="shared" ca="1" si="2"/>
-        <v>46090.369605671294</v>
-      </c>
-      <c r="I7" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" spans="1:9" ht="13.2" x14ac:dyDescent="0.45">
-      <c r="A8" s="3">
-        <v>0</v>
-      </c>
-      <c r="B8" s="3">
+      <c r="F7" s="4" t="n">
+        <f aca="true">NOW()</f>
+        <v>46091.8634306983</v>
+      </c>
+      <c r="G7" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H7" s="4" t="n">
+        <f aca="true">NOW()</f>
+        <v>46091.8634306987</v>
+      </c>
+      <c r="I7" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="B8" s="3" t="n">
         <v>5</v>
       </c>
-      <c r="C8" s="3">
+      <c r="C8" s="3" t="n">
         <v>5</v>
       </c>
-      <c r="D8" s="4">
-        <f t="shared" ca="1" si="0"/>
-        <v>46090.369605671294</v>
+      <c r="D8" s="4" t="n">
+        <f aca="true">NOW()</f>
+        <v>46091.8634306979</v>
       </c>
       <c r="E8" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="F8" s="4">
-        <f t="shared" ca="1" si="1"/>
-        <v>46090.369605671294</v>
-      </c>
-      <c r="G8" s="3">
-        <v>0</v>
-      </c>
-      <c r="H8" s="4">
-        <f t="shared" ca="1" si="2"/>
-        <v>46090.369605671294</v>
-      </c>
-      <c r="I8" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" spans="1:9" ht="13.2" x14ac:dyDescent="0.45">
-      <c r="A9" s="3">
-        <v>0</v>
-      </c>
-      <c r="B9" s="3">
+      <c r="F8" s="4" t="n">
+        <f aca="true">NOW()</f>
+        <v>46091.8634306983</v>
+      </c>
+      <c r="G8" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H8" s="4" t="n">
+        <f aca="true">NOW()</f>
+        <v>46091.8634306988</v>
+      </c>
+      <c r="I8" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="B9" s="3" t="n">
         <v>6</v>
       </c>
-      <c r="C9" s="3">
+      <c r="C9" s="3" t="n">
         <v>6</v>
       </c>
-      <c r="D9" s="4">
-        <f t="shared" ca="1" si="0"/>
-        <v>46090.369605671294</v>
+      <c r="D9" s="4" t="n">
+        <f aca="true">NOW()</f>
+        <v>46091.8634306979</v>
       </c>
       <c r="E9" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="F9" s="4">
-        <f t="shared" ca="1" si="1"/>
-        <v>46090.369605671294</v>
-      </c>
-      <c r="G9" s="3">
-        <v>0</v>
-      </c>
-      <c r="H9" s="4">
-        <f t="shared" ca="1" si="2"/>
-        <v>46090.369605671294</v>
-      </c>
-      <c r="I9" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" spans="1:9" ht="13.2" x14ac:dyDescent="0.45">
-      <c r="A10" s="3">
-        <v>0</v>
-      </c>
-      <c r="B10" s="3">
+      <c r="F9" s="4" t="n">
+        <f aca="true">NOW()</f>
+        <v>46091.8634306983</v>
+      </c>
+      <c r="G9" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H9" s="4" t="n">
+        <f aca="true">NOW()</f>
+        <v>46091.8634306988</v>
+      </c>
+      <c r="I9" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="B10" s="3" t="n">
         <v>7</v>
       </c>
-      <c r="C10" s="3">
+      <c r="C10" s="3" t="n">
         <v>7</v>
       </c>
-      <c r="D10" s="4">
-        <f t="shared" ca="1" si="0"/>
-        <v>46090.369605671294</v>
+      <c r="D10" s="4" t="n">
+        <f aca="true">NOW()</f>
+        <v>46091.863430698</v>
       </c>
       <c r="E10" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="F10" s="4">
-        <f t="shared" ca="1" si="1"/>
-        <v>46090.369605671294</v>
-      </c>
-      <c r="G10" s="3">
-        <v>0</v>
-      </c>
-      <c r="H10" s="4">
-        <f t="shared" ca="1" si="2"/>
-        <v>46090.369605671294</v>
-      </c>
-      <c r="I10" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" spans="1:9" ht="13.2" x14ac:dyDescent="0.45">
-      <c r="A11" s="3">
-        <v>0</v>
-      </c>
-      <c r="B11" s="3">
+      <c r="F10" s="4" t="n">
+        <f aca="true">NOW()</f>
+        <v>46091.8634306984</v>
+      </c>
+      <c r="G10" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H10" s="4" t="n">
+        <f aca="true">NOW()</f>
+        <v>46091.8634306988</v>
+      </c>
+      <c r="I10" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="B11" s="3" t="n">
         <v>8</v>
       </c>
-      <c r="C11" s="3">
+      <c r="C11" s="3" t="n">
         <v>8</v>
       </c>
-      <c r="D11" s="4">
-        <f t="shared" ca="1" si="0"/>
-        <v>46090.369605671294</v>
+      <c r="D11" s="4" t="n">
+        <f aca="true">NOW()</f>
+        <v>46091.863430698</v>
       </c>
       <c r="E11" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="F11" s="4">
-        <f t="shared" ca="1" si="1"/>
-        <v>46090.369605671294</v>
-      </c>
-      <c r="G11" s="3">
-        <v>0</v>
-      </c>
-      <c r="H11" s="4">
-        <f t="shared" ca="1" si="2"/>
-        <v>46090.369605671294</v>
-      </c>
-      <c r="I11" s="3">
+      <c r="F11" s="4" t="n">
+        <f aca="true">NOW()</f>
+        <v>46091.8634306984</v>
+      </c>
+      <c r="G11" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H11" s="4" t="n">
+        <f aca="true">NOW()</f>
+        <v>46091.8634306989</v>
+      </c>
+      <c r="I11" s="3" t="n">
         <v>0</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A2:I3" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
-  <phoneticPr fontId="4"/>
+  <autoFilter ref="A2:I3"/>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
-  <headerFooter>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
     <oddHeader>&amp;R&amp;D &amp;T</oddHeader>
     <oddFooter>&amp;C&amp;P / &amp;N</oddFooter>
   </headerFooter>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>
--- a/.schema/MHR_USER_POS.xlsx
+++ b/.schema/MHR_USER_POS.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\KTC0966\git\sample\.schema\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\t_fuk\git\sample\.schema\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A9DDCBE9-3D7F-40BD-9F9D-0A2BFF9726F7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{78B0CBEC-957A-487D-8A5B-215C4E07B682}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="57480" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="EMARF.MHR_USER_POS" sheetId="1" r:id="rId1"/>
@@ -165,10 +165,10 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyProtection="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment vertical="top" textRotation="180"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment vertical="top" textRotation="180"/>
     </xf>
   </cellXfs>
@@ -488,19 +488,19 @@
       </c>
       <c r="D3" s="3">
         <f t="shared" ref="D3:D12" ca="1" si="0">NOW()</f>
-        <v>46225.643117361113</v>
+        <v>46250.455865162039</v>
       </c>
       <c r="E3" s="4"/>
       <c r="F3" s="3">
         <f t="shared" ref="F3:F12" ca="1" si="1">NOW()</f>
-        <v>46225.643117361113</v>
+        <v>46250.455865162039</v>
       </c>
       <c r="G3" s="2">
         <v>0</v>
       </c>
       <c r="H3" s="3">
         <f t="shared" ref="H3:H12" ca="1" si="2">NOW()</f>
-        <v>46225.643117361113</v>
+        <v>46250.455865162039</v>
       </c>
       <c r="I3" s="2">
         <v>0</v>
@@ -518,19 +518,19 @@
       </c>
       <c r="D4" s="3">
         <f t="shared" ca="1" si="0"/>
-        <v>46225.643117361113</v>
+        <v>46250.455865162039</v>
       </c>
       <c r="E4" s="4"/>
       <c r="F4" s="3">
         <f t="shared" ca="1" si="1"/>
-        <v>46225.643117361113</v>
+        <v>46250.455865162039</v>
       </c>
       <c r="G4" s="2">
         <v>0</v>
       </c>
       <c r="H4" s="3">
         <f t="shared" ca="1" si="2"/>
-        <v>46225.643117361113</v>
+        <v>46250.455865162039</v>
       </c>
       <c r="I4" s="2">
         <v>0</v>
@@ -548,19 +548,19 @@
       </c>
       <c r="D5" s="3">
         <f t="shared" ca="1" si="0"/>
-        <v>46225.643117361113</v>
+        <v>46250.455865162039</v>
       </c>
       <c r="E5" s="4"/>
       <c r="F5" s="3">
         <f t="shared" ca="1" si="1"/>
-        <v>46225.643117361113</v>
+        <v>46250.455865162039</v>
       </c>
       <c r="G5" s="2">
         <v>0</v>
       </c>
       <c r="H5" s="3">
         <f t="shared" ca="1" si="2"/>
-        <v>46225.643117361113</v>
+        <v>46250.455865162039</v>
       </c>
       <c r="I5" s="2">
         <v>0</v>
@@ -578,19 +578,19 @@
       </c>
       <c r="D6" s="3">
         <f t="shared" ca="1" si="0"/>
-        <v>46225.643117361113</v>
+        <v>46250.455865162039</v>
       </c>
       <c r="E6" s="4"/>
       <c r="F6" s="3">
         <f t="shared" ca="1" si="1"/>
-        <v>46225.643117361113</v>
+        <v>46250.455865162039</v>
       </c>
       <c r="G6" s="2">
         <v>0</v>
       </c>
       <c r="H6" s="3">
         <f t="shared" ca="1" si="2"/>
-        <v>46225.643117361113</v>
+        <v>46250.455865162039</v>
       </c>
       <c r="I6" s="2">
         <v>0</v>
@@ -608,19 +608,19 @@
       </c>
       <c r="D7" s="3">
         <f t="shared" ca="1" si="0"/>
-        <v>46225.643117361113</v>
+        <v>46250.455865162039</v>
       </c>
       <c r="E7" s="4"/>
       <c r="F7" s="3">
         <f t="shared" ca="1" si="1"/>
-        <v>46225.643117361113</v>
+        <v>46250.455865162039</v>
       </c>
       <c r="G7" s="2">
         <v>0</v>
       </c>
       <c r="H7" s="3">
         <f t="shared" ca="1" si="2"/>
-        <v>46225.643117361113</v>
+        <v>46250.455865162039</v>
       </c>
       <c r="I7" s="2">
         <v>0</v>
@@ -638,19 +638,19 @@
       </c>
       <c r="D8" s="3">
         <f t="shared" ca="1" si="0"/>
-        <v>46225.643117361113</v>
+        <v>46250.455865162039</v>
       </c>
       <c r="E8" s="4"/>
       <c r="F8" s="3">
         <f t="shared" ca="1" si="1"/>
-        <v>46225.643117361113</v>
+        <v>46250.455865162039</v>
       </c>
       <c r="G8" s="2">
         <v>0</v>
       </c>
       <c r="H8" s="3">
         <f t="shared" ca="1" si="2"/>
-        <v>46225.643117361113</v>
+        <v>46250.455865162039</v>
       </c>
       <c r="I8" s="2">
         <v>0</v>
@@ -668,19 +668,19 @@
       </c>
       <c r="D9" s="3">
         <f t="shared" ca="1" si="0"/>
-        <v>46225.643117361113</v>
+        <v>46250.455865162039</v>
       </c>
       <c r="E9" s="4"/>
       <c r="F9" s="3">
         <f t="shared" ca="1" si="1"/>
-        <v>46225.643117361113</v>
+        <v>46250.455865162039</v>
       </c>
       <c r="G9" s="2">
         <v>0</v>
       </c>
       <c r="H9" s="3">
         <f t="shared" ca="1" si="2"/>
-        <v>46225.643117361113</v>
+        <v>46250.455865162039</v>
       </c>
       <c r="I9" s="2">
         <v>0</v>
@@ -698,19 +698,19 @@
       </c>
       <c r="D10" s="3">
         <f t="shared" ca="1" si="0"/>
-        <v>46225.643117361113</v>
+        <v>46250.455865162039</v>
       </c>
       <c r="E10" s="4"/>
       <c r="F10" s="3">
         <f t="shared" ca="1" si="1"/>
-        <v>46225.643117361113</v>
+        <v>46250.455865162039</v>
       </c>
       <c r="G10" s="2">
         <v>0</v>
       </c>
       <c r="H10" s="3">
         <f t="shared" ca="1" si="2"/>
-        <v>46225.643117361113</v>
+        <v>46250.455865162039</v>
       </c>
       <c r="I10" s="2">
         <v>0</v>
@@ -728,19 +728,19 @@
       </c>
       <c r="D11" s="3">
         <f t="shared" ca="1" si="0"/>
-        <v>46225.643117361113</v>
+        <v>46250.455865162039</v>
       </c>
       <c r="E11" s="4"/>
       <c r="F11" s="3">
         <f t="shared" ca="1" si="1"/>
-        <v>46225.643117361113</v>
+        <v>46250.455865162039</v>
       </c>
       <c r="G11" s="2">
         <v>0</v>
       </c>
       <c r="H11" s="3">
         <f t="shared" ca="1" si="2"/>
-        <v>46225.643117361113</v>
+        <v>46250.455865162039</v>
       </c>
       <c r="I11" s="2">
         <v>0</v>
@@ -758,19 +758,19 @@
       </c>
       <c r="D12" s="3">
         <f t="shared" ca="1" si="0"/>
-        <v>46225.643117361113</v>
+        <v>46250.455865162039</v>
       </c>
       <c r="E12" s="4"/>
       <c r="F12" s="3">
         <f t="shared" ca="1" si="1"/>
-        <v>46225.643117361113</v>
+        <v>46250.455865162039</v>
       </c>
       <c r="G12" s="2">
         <v>0</v>
       </c>
       <c r="H12" s="3">
         <f t="shared" ca="1" si="2"/>
-        <v>46225.643117361113</v>
+        <v>46250.455865162039</v>
       </c>
       <c r="I12" s="2">
         <v>0</v>
